--- a/banks/W17_Kahoot匯入.xlsx
+++ b/banks/W17_Kahoot匯入.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -491,30 +491,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>瘦體素</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>代謝症候群</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>代謝整合</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>飽食狀態</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>瘦體素</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>代謝症候群</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>代謝整合</t>
-        </is>
-      </c>
       <c r="F2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -526,30 +526,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>激素</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>受體</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>血糖</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>胰島素</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>激素</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>血糖</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -561,30 +561,30 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>肝臟</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>受體</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>恆定</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>肝臟</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>激素</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>受體</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -596,30 +596,30 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>飽食狀態</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>骨骼肌</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>飽食狀態</t>
-        </is>
-      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>代謝整合</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>訊息傳遞</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>代謝整合</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -636,14 +636,14 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>胰島素阻抗</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>第二傳訊者</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>胰島素阻抗</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>脂肪組織</t>
@@ -654,7 +654,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -666,12 +666,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>糖尿病</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>飽食狀態</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>糖尿病</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -706,17 +706,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>血糖</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>升糖素</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>脂肪組織</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>升糖素</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>血糖</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -736,30 +736,30 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>飢餓狀態</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>腎上腺素</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>飢餓狀態</t>
-        </is>
-      </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>訊息傳遞</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>脂肪組織</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>訊息傳遞</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -771,30 +771,30 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>恆定</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>瘦體素</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>皮質醇</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>胰島素</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>皮質醇</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>瘦體素</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>恆定</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -811,17 +811,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>脂肪組織</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>骨骼肌</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>肝臟</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>脂肪組織</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -841,19 +841,19 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>恆定</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>受體</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>血糖</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>恆定</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>受體</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>皮質醇</t>
@@ -864,7 +864,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -876,30 +876,30 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>恆定</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>骨骼肌</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>皮質醇</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>受體</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>皮質醇</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>恆定</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>骨骼肌</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -911,17 +911,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>骨骼肌</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>糖尿病</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>腎上腺素</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>骨骼肌</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -946,30 +946,30 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>皮質醇</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>脂肪組織</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>代謝症候群</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>飢餓狀態</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>脂肪組織</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>皮質醇</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>代謝症候群</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -981,30 +981,30 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>飢餓狀態</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>脂肪組織</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>糖尿病</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>皮質醇</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>糖尿病</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>脂肪組織</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>飢餓狀態</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1016,19 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>血糖</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>皮質醇</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>肝臟</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>血糖</t>
-        </is>
-      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>恆定</t>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1051,30 +1051,30 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>受體</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>骨骼肌</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>訊息傳遞</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>受體</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>皮質醇</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>骨骼肌</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1086,30 +1086,30 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>骨骼肌</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>肝臟</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>胰島素</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>糖尿病</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>肝臟</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>骨骼肌</t>
-        </is>
-      </c>
       <c r="F19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1121,30 +1121,30 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>脂肪組織</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>飽食狀態</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>皮質醇</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>胰島素阻抗</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>脂肪組織</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>飽食狀態</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1178,6 +1178,146 @@
         <v>30</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:w17_organs_labeled) 標號2是哪個器官?</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>肝臟</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>骨骼肌</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>腦</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>脂肪組織</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:w17_fed_fasted_labeled) 標號4(飢餓狀態肝臟)何種作用增強?</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>醣解作用</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>肝醣分解</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>脂質新生</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>蛋白質合成</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>哪一個配對正確?</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>瘦體素—由胰臟分泌調控血糖</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>升糖素—刺激肝醣分解與醣質新生</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>腎上腺素—抑制肝醣分解</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>胰島素—刺激脂肪分解</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>長期飢餓狀態下，腦部主要能量來源會轉換成什麼?</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>酮體</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>葡萄糖</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>乳酸</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>游離脂肪酸</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
